--- a/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
+++ b/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
@@ -47,7 +47,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>ANITEC</t>
+    <t>GOV-CR</t>
   </si>
   <si>
     <t>leocadio.macambira</t>
@@ -59,10 +59,10 @@
     <t>118.229.998-98</t>
   </si>
   <si>
-    <t>leocadio.macambira@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>PRESI</t>
+    <t>leocadio.macambira@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>GABIN</t>
   </si>
   <si>
     <t>Básico</t>
@@ -80,10 +80,10 @@
     <t>124.039.082-31</t>
   </si>
   <si>
-    <t>tertuliano.gongora@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>PROT</t>
+    <t>tertuliano.gongora@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>SEADM</t>
   </si>
   <si>
     <t>3</t>
@@ -98,7 +98,7 @@
     <t>147.551.240-69</t>
   </si>
   <si>
-    <t>belarmina.batatinha@anitec.gov.br</t>
+    <t>belarmina.batatinha@cariris.gov.br</t>
   </si>
   <si>
     <t>Colaborador (Básico sem Assinatura)</t>
@@ -116,10 +116,10 @@
     <t>836.508.748-06</t>
   </si>
   <si>
-    <t>raimundo.viriato@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>COEST</t>
+    <t>raimundo.viriato@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>ESPRE</t>
   </si>
   <si>
     <t>5</t>
@@ -134,10 +134,10 @@
     <t>065.697.139-81</t>
   </si>
   <si>
-    <t>ursula.trigueirinho@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>DIEXP</t>
+    <t>ursula.trigueirinho@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>SUINV</t>
   </si>
   <si>
     <t>6</t>
@@ -152,7 +152,7 @@
     <t>881.174.108-42</t>
   </si>
   <si>
-    <t>inocencio.galhardo@anitec.gov.br</t>
+    <t>inocencio.galhardo@cariris.gov.br</t>
   </si>
   <si>
     <t>7</t>
@@ -167,7 +167,7 @@
     <t>849.924.536-60</t>
   </si>
   <si>
-    <t>querubina.espinosa@anitec.gov.br</t>
+    <t>querubina.espinosa@cariris.gov.br</t>
   </si>
   <si>
     <t>8</t>
@@ -182,7 +182,7 @@
     <t>900.079.227-44</t>
   </si>
   <si>
-    <t>dionisia.barraginha@anitec.gov.br</t>
+    <t>dionisia.barraginha@cariris.gov.br</t>
   </si>
   <si>
     <t>9</t>
@@ -197,7 +197,7 @@
     <t>852.721.021-50</t>
   </si>
   <si>
-    <t>jocelina.pedregulho@anitec.gov.br</t>
+    <t>jocelina.pedregulho@cariris.gov.br</t>
   </si>
   <si>
     <t>10</t>
@@ -212,10 +212,10 @@
     <t>251.749.928-44</t>
   </si>
   <si>
-    <t>cipriano.xavier@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>ARQ</t>
+    <t>cipriano.xavier@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>COPAR</t>
   </si>
   <si>
     <t>11</t>
@@ -233,7 +233,7 @@
     <t>951.628.492-27</t>
   </si>
   <si>
-    <t>zildette.brazil@anitec.gov.br</t>
+    <t>zildette.brazil@cariris.gov.br</t>
   </si>
   <si>
     <t>12</t>
@@ -248,7 +248,7 @@
     <t>321.124.828-58</t>
   </si>
   <si>
-    <t>virgulino.beringela@anitec.gov.br</t>
+    <t>virgulino.beringela@cariris.gov.br</t>
   </si>
   <si>
     <t>13</t>
@@ -263,7 +263,7 @@
     <t>336.202.881-00</t>
   </si>
   <si>
-    <t>hemengarda.quaresmeira@anitec.gov.br</t>
+    <t>hemengarda.quaresmeira@cariris.gov.br</t>
   </si>
   <si>
     <t>14</t>
@@ -278,10 +278,10 @@
     <t>644.042.918-33</t>
   </si>
   <si>
-    <t>sebastiana.fagundes@anitec.gov.br</t>
-  </si>
-  <si>
-    <t>CGADE</t>
+    <t>sebastiana.fagundes@cariris.gov.br</t>
+  </si>
+  <si>
+    <t>SUGEP</t>
   </si>
   <si>
     <t>15</t>
@@ -296,7 +296,7 @@
     <t>951.190.527-97</t>
   </si>
   <si>
-    <t>aparicio.caramuru@anitec.gov.br</t>
+    <t>aparicio.caramuru@cariris.gov.br</t>
   </si>
   <si>
     <t>16</t>
@@ -311,7 +311,7 @@
     <t>188.649.230-12</t>
   </si>
   <si>
-    <t>eustaquio.sapopemba@anitec.gov.br</t>
+    <t>eustaquio.sapopemba@cariris.gov.br</t>
   </si>
   <si>
     <t>17</t>
@@ -326,7 +326,7 @@
     <t>073.524.764-15</t>
   </si>
   <si>
-    <t>ubaldo.garrincha@anitec.gov.br</t>
+    <t>ubaldo.garrincha@cariris.gov.br</t>
   </si>
   <si>
     <t>18</t>
@@ -341,7 +341,7 @@
     <t>388.632.769-86</t>
   </si>
   <si>
-    <t>waldemira.catunda@anitec.gov.br</t>
+    <t>waldemira.catunda@cariris.gov.br</t>
   </si>
   <si>
     <t>19</t>
@@ -356,7 +356,7 @@
     <t>931.047.073-91</t>
   </si>
   <si>
-    <t>genoveva.montenegro@anitec.gov.br</t>
+    <t>genoveva.montenegro@cariris.gov.br</t>
   </si>
   <si>
     <t>20</t>
@@ -371,7 +371,7 @@
     <t>586.632.848-88</t>
   </si>
   <si>
-    <t>madalena.assombracao@anitec.gov.br</t>
+    <t>madalena.assombracao@cariris.gov.br</t>
   </si>
   <si>
     <t>21</t>
@@ -386,7 +386,7 @@
     <t>305.651.755-99</t>
   </si>
   <si>
-    <t>osvalda.anzois@anitec.gov.br</t>
+    <t>osvalda.anzois@cariris.gov.br</t>
   </si>
   <si>
     <t>22</t>
@@ -401,7 +401,7 @@
     <t>302.612.775-29</t>
   </si>
   <si>
-    <t>praxedes.furquim@anitec.gov.br</t>
+    <t>praxedes.furquim@cariris.gov.br</t>
   </si>
   <si>
     <t>23</t>
@@ -416,7 +416,7 @@
     <t>174.402.002-76</t>
   </si>
   <si>
-    <t>feliciana.travassos@anitec.gov.br</t>
+    <t>feliciana.travassos@cariris.gov.br</t>
   </si>
   <si>
     <t>24</t>
@@ -431,7 +431,7 @@
     <t>750.860.800-37</t>
   </si>
   <si>
-    <t>zacarias.jatoba@anitec.gov.br</t>
+    <t>zacarias.jatoba@cariris.gov.br</t>
   </si>
   <si>
     <t>25</t>
@@ -446,7 +446,7 @@
     <t>608.053.040-61</t>
   </si>
   <si>
-    <t>adroaldo.tamborete@anitec.gov.br</t>
+    <t>adroaldo.tamborete@cariris.gov.br</t>
   </si>
 </sst>
 </file>

--- a/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
+++ b/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>0.Index</t>
   </si>
@@ -44,10 +44,7 @@
     <t>8.perfilPrimeiraPermissao</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>GOV-CR</t>
+    <t>ABC</t>
   </si>
   <si>
     <t>leocadio.macambira</t>
@@ -59,7 +56,7 @@
     <t>118.229.998-98</t>
   </si>
   <si>
-    <t>leocadio.macambira@cariris.gov.br</t>
+    <t>leocadio.macambira@abc.gov.br</t>
   </si>
   <si>
     <t>GABIN</t>
@@ -68,9 +65,6 @@
     <t>Básico</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>tertuliano.gongora</t>
   </si>
   <si>
@@ -80,15 +74,12 @@
     <t>124.039.082-31</t>
   </si>
   <si>
-    <t>tertuliano.gongora@cariris.gov.br</t>
+    <t>tertuliano.gongora@abc.gov.br</t>
   </si>
   <si>
     <t>SEADM</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>belarmina.batatinha</t>
   </si>
   <si>
@@ -98,15 +89,12 @@
     <t>147.551.240-69</t>
   </si>
   <si>
-    <t>belarmina.batatinha@cariris.gov.br</t>
+    <t>belarmina.batatinha@abc.gov.br</t>
   </si>
   <si>
     <t>Colaborador (Básico sem Assinatura)</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>raimundo.viriato</t>
   </si>
   <si>
@@ -116,15 +104,12 @@
     <t>836.508.748-06</t>
   </si>
   <si>
-    <t>raimundo.viriato@cariris.gov.br</t>
+    <t>raimundo.viriato@abc.gov.br</t>
   </si>
   <si>
     <t>ESPRE</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>ursula.trigueirinho</t>
   </si>
   <si>
@@ -134,15 +119,12 @@
     <t>065.697.139-81</t>
   </si>
   <si>
-    <t>ursula.trigueirinho@cariris.gov.br</t>
+    <t>ursula.trigueirinho@abc.gov.br</t>
   </si>
   <si>
     <t>SUINV</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>inocencio.galhardo</t>
   </si>
   <si>
@@ -152,10 +134,7 @@
     <t>881.174.108-42</t>
   </si>
   <si>
-    <t>inocencio.galhardo@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>inocencio.galhardo@abc.gov.br</t>
   </si>
   <si>
     <t>querubina.espinosa</t>
@@ -167,10 +146,7 @@
     <t>849.924.536-60</t>
   </si>
   <si>
-    <t>querubina.espinosa@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>querubina.espinosa@abc.gov.br</t>
   </si>
   <si>
     <t>dionisia.barraginha</t>
@@ -182,10 +158,7 @@
     <t>900.079.227-44</t>
   </si>
   <si>
-    <t>dionisia.barraginha@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>dionisia.barraginha@abc.gov.br</t>
   </si>
   <si>
     <t>jocelina.pedregulho</t>
@@ -197,10 +170,7 @@
     <t>852.721.021-50</t>
   </si>
   <si>
-    <t>jocelina.pedregulho@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>jocelina.pedregulho@abc.gov.br</t>
   </si>
   <si>
     <t>cipriano.xavier</t>
@@ -212,15 +182,12 @@
     <t>251.749.928-44</t>
   </si>
   <si>
-    <t>cipriano.xavier@cariris.gov.br</t>
+    <t>cipriano.xavier@abc.gov.br</t>
   </si>
   <si>
     <t>COPAR</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>norberto.camarinha</t>
   </si>
   <si>
@@ -233,10 +200,7 @@
     <t>951.628.492-27</t>
   </si>
   <si>
-    <t>zildette.brazil@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>zildette.brazil@abc.gov.br</t>
   </si>
   <si>
     <t>virgulino.beringela</t>
@@ -248,10 +212,7 @@
     <t>321.124.828-58</t>
   </si>
   <si>
-    <t>virgulino.beringela@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>virgulino.beringela@abc.gov.br</t>
   </si>
   <si>
     <t>hemengarda.quaresmeira</t>
@@ -263,10 +224,7 @@
     <t>336.202.881-00</t>
   </si>
   <si>
-    <t>hemengarda.quaresmeira@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>hemengarda.quaresmeira@abc.gov.br</t>
   </si>
   <si>
     <t>sebastiana.fagundes</t>
@@ -278,15 +236,12 @@
     <t>644.042.918-33</t>
   </si>
   <si>
-    <t>sebastiana.fagundes@cariris.gov.br</t>
+    <t>sebastiana.fagundes@abc.gov.br</t>
   </si>
   <si>
     <t>SUGEP</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>aparicio.caramuru</t>
   </si>
   <si>
@@ -296,10 +251,7 @@
     <t>951.190.527-97</t>
   </si>
   <si>
-    <t>aparicio.caramuru@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>aparicio.caramuru@abc.gov.br</t>
   </si>
   <si>
     <t>eustaquio.sapopemba</t>
@@ -311,10 +263,7 @@
     <t>188.649.230-12</t>
   </si>
   <si>
-    <t>eustaquio.sapopemba@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>eustaquio.sapopemba@abc.gov.br</t>
   </si>
   <si>
     <t>ubaldo.garrincha</t>
@@ -326,10 +275,7 @@
     <t>073.524.764-15</t>
   </si>
   <si>
-    <t>ubaldo.garrincha@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>ubaldo.garrincha@abc.gov.br</t>
   </si>
   <si>
     <t>waldemira.catunda</t>
@@ -341,10 +287,7 @@
     <t>388.632.769-86</t>
   </si>
   <si>
-    <t>waldemira.catunda@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>waldemira.catunda@abc.gov.br</t>
   </si>
   <si>
     <t>genoveva.montenegro</t>
@@ -356,10 +299,7 @@
     <t>931.047.073-91</t>
   </si>
   <si>
-    <t>genoveva.montenegro@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>genoveva.montenegro@abc.gov.br</t>
   </si>
   <si>
     <t>madalena.assombracao</t>
@@ -371,10 +311,7 @@
     <t>586.632.848-88</t>
   </si>
   <si>
-    <t>madalena.assombracao@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>madalena.assombracao@abc.gov.br</t>
   </si>
   <si>
     <t>osvalda.anzois</t>
@@ -386,10 +323,7 @@
     <t>305.651.755-99</t>
   </si>
   <si>
-    <t>osvalda.anzois@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>osvalda.anzois@abc.gov.br</t>
   </si>
   <si>
     <t>praxedes.furquim</t>
@@ -401,10 +335,7 @@
     <t>302.612.775-29</t>
   </si>
   <si>
-    <t>praxedes.furquim@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>praxedes.furquim@abc.gov.br</t>
   </si>
   <si>
     <t>feliciana.travassos</t>
@@ -416,10 +347,7 @@
     <t>174.402.002-76</t>
   </si>
   <si>
-    <t>feliciana.travassos@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>feliciana.travassos@abc.gov.br</t>
   </si>
   <si>
     <t>zacarias.jatoba</t>
@@ -431,10 +359,7 @@
     <t>750.860.800-37</t>
   </si>
   <si>
-    <t>zacarias.jatoba@cariris.gov.br</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>zacarias.jatoba@abc.gov.br</t>
   </si>
   <si>
     <t>adroaldo.tamborete</t>
@@ -446,7 +371,7 @@
     <t>608.053.040-61</t>
   </si>
   <si>
-    <t>adroaldo.tamborete@cariris.gov.br</t>
+    <t>adroaldo.tamborete@abc.gov.br</t>
   </si>
 </sst>
 </file>
@@ -818,680 +743,680 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="0" t="s">
-        <v>9</v>
+      <c r="A2" s="0">
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="H2" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="0" t="s">
+      <c r="D3" s="0" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>19</v>
       </c>
       <c r="E3" s="0"/>
       <c r="F3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="I3" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="D4" s="0" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="0"/>
       <c r="F4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="D5" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>31</v>
       </c>
       <c r="E5" s="0"/>
       <c r="F5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>37</v>
       </c>
       <c r="E6" s="0"/>
       <c r="F6" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="0" t="s">
-        <v>41</v>
+      <c r="A7" s="0">
+        <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E7" s="0"/>
       <c r="F7" s="0" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>47</v>
-      </c>
       <c r="D8" s="0" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E8" s="0"/>
       <c r="F8" s="0" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="0" t="s">
-        <v>51</v>
+      <c r="A9" s="0">
+        <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E9" s="0"/>
       <c r="F9" s="0" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="0" t="s">
-        <v>56</v>
+      <c r="A10" s="0">
+        <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E10" s="0"/>
       <c r="F10" s="0" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="0" t="s">
-        <v>61</v>
+      <c r="A11" s="0">
+        <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E11" s="0"/>
       <c r="F11" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="0" t="s">
-        <v>67</v>
+      <c r="A12" s="0">
+        <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="0" t="s">
-        <v>73</v>
+      <c r="A13" s="0">
+        <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E13" s="0"/>
       <c r="F13" s="0" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="0" t="s">
-        <v>78</v>
+      <c r="A14" s="0">
+        <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E14" s="0"/>
       <c r="F14" s="0" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="0" t="s">
-        <v>83</v>
+      <c r="A15" s="0">
+        <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E15" s="0"/>
       <c r="F15" s="0" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="0" t="s">
-        <v>89</v>
+      <c r="A16" s="0">
+        <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E16" s="0"/>
       <c r="F16" s="0" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I16" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="0">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="0" t="s">
-        <v>94</v>
-      </c>
       <c r="B17" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E17" s="0"/>
       <c r="F17" s="0" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="0" t="s">
-        <v>99</v>
+      <c r="A18" s="0">
+        <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E18" s="0"/>
       <c r="F18" s="0" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H18" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="0">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="0" t="s">
         <v>88</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>106</v>
       </c>
       <c r="E19" s="0"/>
       <c r="F19" s="0" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="0" t="s">
-        <v>109</v>
+      <c r="A20" s="0">
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E20" s="0"/>
       <c r="F20" s="0" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="0" t="s">
-        <v>114</v>
+      <c r="A21" s="0">
+        <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E21" s="0"/>
       <c r="F21" s="0" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="0" t="s">
-        <v>119</v>
+      <c r="A22" s="0">
+        <v>21</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="E22" s="0"/>
       <c r="F22" s="0" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="H22" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="0">
         <v>22</v>
       </c>
-      <c r="I22" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="0" t="s">
-        <v>124</v>
-      </c>
       <c r="B23" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E23" s="0"/>
       <c r="F23" s="0" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="0" t="s">
-        <v>129</v>
+      <c r="A24" s="0">
+        <v>23</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E24" s="0"/>
       <c r="F24" s="0" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="0" t="s">
-        <v>134</v>
+      <c r="A25" s="0">
+        <v>24</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E25" s="0"/>
       <c r="F25" s="0" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="0" t="s">
-        <v>139</v>
+      <c r="A26" s="0">
+        <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="E26" s="0"/>
       <c r="F26" s="0" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
+++ b/sip/web/modulos/cargaEmLote/sipCargaEmLote/exemplos/exemploUsuarios.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
   <si>
     <t>0.Index</t>
   </si>
@@ -44,6 +44,9 @@
     <t>8.perfilPrimeiraPermissao</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>ABC</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
     <t>Básico</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>tertuliano.gongora</t>
   </si>
   <si>
@@ -80,6 +86,9 @@
     <t>SEADM</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>belarmina.batatinha</t>
   </si>
   <si>
@@ -95,6 +104,9 @@
     <t>Colaborador (Básico sem Assinatura)</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>raimundo.viriato</t>
   </si>
   <si>
@@ -110,6 +122,9 @@
     <t>ESPRE</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>ursula.trigueirinho</t>
   </si>
   <si>
@@ -125,6 +140,9 @@
     <t>SUINV</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>inocencio.galhardo</t>
   </si>
   <si>
@@ -137,6 +155,9 @@
     <t>inocencio.galhardo@abc.gov.br</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>querubina.espinosa</t>
   </si>
   <si>
@@ -149,6 +170,9 @@
     <t>querubina.espinosa@abc.gov.br</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>dionisia.barraginha</t>
   </si>
   <si>
@@ -161,6 +185,9 @@
     <t>dionisia.barraginha@abc.gov.br</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>jocelina.pedregulho</t>
   </si>
   <si>
@@ -173,6 +200,9 @@
     <t>jocelina.pedregulho@abc.gov.br</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>cipriano.xavier</t>
   </si>
   <si>
@@ -188,6 +218,9 @@
     <t>COPAR</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>norberto.camarinha</t>
   </si>
   <si>
@@ -203,6 +236,9 @@
     <t>zildette.brazil@abc.gov.br</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>virgulino.beringela</t>
   </si>
   <si>
@@ -215,6 +251,9 @@
     <t>virgulino.beringela@abc.gov.br</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>hemengarda.quaresmeira</t>
   </si>
   <si>
@@ -227,6 +266,9 @@
     <t>hemengarda.quaresmeira@abc.gov.br</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>sebastiana.fagundes</t>
   </si>
   <si>
@@ -242,6 +284,9 @@
     <t>SUGEP</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>aparicio.caramuru</t>
   </si>
   <si>
@@ -254,6 +299,9 @@
     <t>aparicio.caramuru@abc.gov.br</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>eustaquio.sapopemba</t>
   </si>
   <si>
@@ -266,6 +314,9 @@
     <t>eustaquio.sapopemba@abc.gov.br</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>ubaldo.garrincha</t>
   </si>
   <si>
@@ -278,6 +329,9 @@
     <t>ubaldo.garrincha@abc.gov.br</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>waldemira.catunda</t>
   </si>
   <si>
@@ -290,6 +344,9 @@
     <t>waldemira.catunda@abc.gov.br</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>genoveva.montenegro</t>
   </si>
   <si>
@@ -302,6 +359,9 @@
     <t>genoveva.montenegro@abc.gov.br</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>madalena.assombracao</t>
   </si>
   <si>
@@ -314,6 +374,9 @@
     <t>madalena.assombracao@abc.gov.br</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>osvalda.anzois</t>
   </si>
   <si>
@@ -326,6 +389,9 @@
     <t>osvalda.anzois@abc.gov.br</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>praxedes.furquim</t>
   </si>
   <si>
@@ -338,6 +404,9 @@
     <t>praxedes.furquim@abc.gov.br</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>feliciana.travassos</t>
   </si>
   <si>
@@ -350,6 +419,9 @@
     <t>feliciana.travassos@abc.gov.br</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>zacarias.jatoba</t>
   </si>
   <si>
@@ -360,6 +432,9 @@
   </si>
   <si>
     <t>zacarias.jatoba@abc.gov.br</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>adroaldo.tamborete</t>
@@ -743,680 +818,680 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="0">
-        <v>1</v>
+      <c r="A2" s="0" t="s">
+        <v>9</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="0">
-        <v>2</v>
+      <c r="A3" s="0" t="s">
+        <v>17</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="0"/>
       <c r="F3" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="0">
-        <v>3</v>
+      <c r="A4" s="0" t="s">
+        <v>23</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="0"/>
       <c r="F4" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="0">
-        <v>4</v>
+      <c r="A5" s="0" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="0"/>
       <c r="F5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="0">
-        <v>5</v>
+      <c r="A6" s="0" t="s">
+        <v>35</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="0"/>
       <c r="F6" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="0">
-        <v>6</v>
+      <c r="A7" s="0" t="s">
+        <v>41</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7" s="0"/>
       <c r="F7" s="0" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="0">
-        <v>7</v>
+      <c r="A8" s="0" t="s">
+        <v>46</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E8" s="0"/>
       <c r="F8" s="0" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="0">
-        <v>8</v>
+      <c r="A9" s="0" t="s">
+        <v>51</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E9" s="0"/>
       <c r="F9" s="0" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="0">
-        <v>9</v>
+      <c r="A10" s="0" t="s">
+        <v>56</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E10" s="0"/>
       <c r="F10" s="0" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="0">
-        <v>10</v>
+      <c r="A11" s="0" t="s">
+        <v>61</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E11" s="0"/>
       <c r="F11" s="0" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="0">
-        <v>11</v>
+      <c r="A12" s="0" t="s">
+        <v>67</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="0">
-        <v>12</v>
+      <c r="A13" s="0" t="s">
+        <v>73</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E13" s="0"/>
       <c r="F13" s="0" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="0">
-        <v>13</v>
+      <c r="A14" s="0" t="s">
+        <v>78</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E14" s="0"/>
       <c r="F14" s="0" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="0">
-        <v>14</v>
+      <c r="A15" s="0" t="s">
+        <v>83</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E15" s="0"/>
       <c r="F15" s="0" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="0">
-        <v>15</v>
+      <c r="A16" s="0" t="s">
+        <v>89</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E16" s="0"/>
       <c r="F16" s="0" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="0">
-        <v>16</v>
+      <c r="A17" s="0" t="s">
+        <v>94</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E17" s="0"/>
       <c r="F17" s="0" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="0">
-        <v>17</v>
+      <c r="A18" s="0" t="s">
+        <v>99</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E18" s="0"/>
       <c r="F18" s="0" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="0">
-        <v>18</v>
+      <c r="A19" s="0" t="s">
+        <v>104</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E19" s="0"/>
       <c r="F19" s="0" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="0">
-        <v>19</v>
+      <c r="A20" s="0" t="s">
+        <v>109</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E20" s="0"/>
       <c r="F20" s="0" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="0">
-        <v>20</v>
+      <c r="A21" s="0" t="s">
+        <v>114</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E21" s="0"/>
       <c r="F21" s="0" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="0">
-        <v>21</v>
+      <c r="A22" s="0" t="s">
+        <v>119</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E22" s="0"/>
       <c r="F22" s="0" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="0">
-        <v>22</v>
+      <c r="A23" s="0" t="s">
+        <v>124</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E23" s="0"/>
       <c r="F23" s="0" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="0">
-        <v>23</v>
+      <c r="A24" s="0" t="s">
+        <v>129</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E24" s="0"/>
       <c r="F24" s="0" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="0">
-        <v>24</v>
+      <c r="A25" s="0" t="s">
+        <v>134</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E25" s="0"/>
       <c r="F25" s="0" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="0">
-        <v>25</v>
+      <c r="A26" s="0" t="s">
+        <v>139</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="E26" s="0"/>
       <c r="F26" s="0" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
